--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486381_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486381_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1306</v>
+        <v>4.5957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.848</v>
+        <v>2.5403</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2826</v>
+        <v>2.0553</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0023</v>
+        <v>4.8737</v>
       </c>
       <c r="H2" t="n">
-        <v>1.788</v>
+        <v>0.3523</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7857</v>
+        <v>4.5214</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5816</v>
+        <v>3.6062</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8432</v>
+        <v>1.022</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.4248</v>
+        <v>2.5843</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5839</v>
+        <v>1.2675</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0552</v>
+        <v>-0.6696</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6391</v>
+        <v>1.9371</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6508</v>
+        <v>0.0384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2572</v>
+        <v>0.0216</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3937</v>
+        <v>0.0168</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2599</v>
+        <v>-0.3165</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7283</v>
+        <v>4.4093</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0428</v>
+        <v>0.9417</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6855</v>
+        <v>3.4676</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8737</v>
+        <v>1.0023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3523</v>
+        <v>1.788</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5214</v>
+        <v>-0.7857</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6062</v>
+        <v>-0.5816</v>
       </c>
       <c r="K3" t="n">
-        <v>1.022</v>
+        <v>1.8432</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5843</v>
+        <v>-2.4248</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2675</v>
+        <v>1.5839</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6696</v>
+        <v>-0.0552</v>
       </c>
       <c r="O3" t="n">
-        <v>1.9371</v>
+        <v>1.6391</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8289</v>
+        <v>0.9295</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4759</v>
+        <v>0.3509</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3531</v>
+        <v>0.5786</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3165</v>
+        <v>2.2599</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6111</v>
+        <v>1.6248</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2321</v>
+        <v>-0.9492</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.621</v>
+        <v>2.574</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7129</v>
+        <v>-0.6543</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4562</v>
+        <v>-1.4233</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1691</v>
+        <v>0.769</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1635</v>
+        <v>-1.5242</v>
       </c>
       <c r="K4" t="n">
-        <v>2.251</v>
+        <v>-1.3346</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9125</v>
+        <v>-0.1896</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4506</v>
+        <v>0.8699</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7072</v>
+        <v>-0.0887</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2566</v>
+        <v>0.9586</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6525</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-5.4377</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3463</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2882</v>
+        <v>-0.0276</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0581</v>
+        <v>0.7378</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7955</v>
+        <v>5.919</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>6.0403</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.751</v>
+        <v>-0.1213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1986</v>
+        <v>1.5929</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8685</v>
+        <v>-1.1228</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0672</v>
+        <v>2.7157</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6543</v>
+        <v>0.7761</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4233</v>
+        <v>-0.5387</v>
       </c>
       <c r="I5" t="n">
-        <v>0.769</v>
+        <v>1.3148</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5242</v>
+        <v>-0.1759</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3346</v>
+        <v>-0.2341</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1896</v>
+        <v>0.0582</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8699</v>
+        <v>0.952</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0887</v>
+        <v>-0.3047</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9586</v>
+        <v>1.2566</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.3501</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.4377</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2841</v>
+        <v>0.1643</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9469</v>
+        <v>0.1406</v>
       </c>
       <c r="U5" t="n">
-        <v>1.231</v>
+        <v>0.0237</v>
       </c>
       <c r="V5" t="n">
-        <v>5.919</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>6.0403</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2126</v>
+        <v>0.8077</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2126</v>
+        <v>-2.0833</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5475</v>
+        <v>2.7129</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5475</v>
+        <v>-0.4562</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.1691</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4.1635</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.251</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.9125</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5475</v>
+        <v>-1.4506</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5475</v>
+        <v>-2.7072</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.2566</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0205</v>
+        <v>0.5429</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0529</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0205</v>
+        <v>0.5957</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7395</v>
+        <v>-1.7955</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7395</v>
+        <v>-2.751</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.019</v>
+        <v>0.2434</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1456</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1646</v>
+        <v>0.2434</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8253</v>
+        <v>-0.5475</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3017</v>
+        <v>-0.5475</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5235</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3201</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5052</v>
+        <v>-0.5475</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0582</v>
+        <v>-0.5475</v>
       </c>
       <c r="O7" t="n">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9576</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.216</v>
+        <v>0.0514</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0791</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1369</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0647</v>
+        <v>0.7395</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.695</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1676</v>
+        <v>-0.8514</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3594</v>
+        <v>-1.4304</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1917</v>
+        <v>0.579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7761</v>
+        <v>1.8253</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5387</v>
+        <v>1.3017</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3148</v>
+        <v>0.5235</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1759</v>
+        <v>0.3201</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2341</v>
+        <v>0.2436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0582</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.952</v>
+        <v>1.5052</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3047</v>
+        <v>1.0582</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2566</v>
+        <v>0.447</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5962</v>
+        <v>1.3456</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0959</v>
+        <v>0.7943</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5003</v>
+        <v>0.5513</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.0647</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7038</v>
+        <v>-1.4388</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.148</v>
+        <v>-1.1913</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5558</v>
+        <v>-0.2476</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1596</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3906</v>
+        <v>0.6555</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2656</v>
+        <v>0.2223</v>
       </c>
       <c r="U9" t="n">
-        <v>0.125</v>
+        <v>0.4332</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3698</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2403</v>
+        <v>-1.5454</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4905</v>
+        <v>-0.9497</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7498</v>
+        <v>-0.5957</v>
       </c>
       <c r="G10" t="n">
         <v>0.1898</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4813</v>
+        <v>0.2136</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.399</v>
+        <v>0.1418</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0823</v>
+        <v>0.0718</v>
       </c>
       <c r="V10" t="n">
         <v>0.4437</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6362</v>
+        <v>-5.5733</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0993</v>
+        <v>-5.0056</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5369</v>
+        <v>-0.5677</v>
       </c>
       <c r="G11" t="n">
         <v>-2.278</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.483</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3461</v>
+        <v>0.4398</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1369</v>
+        <v>0.106</v>
       </c>
       <c r="V11" t="n">
         <v>0.074</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.152300000000003</v>
+        <v>3.864899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9884</v>
+        <v>-4.276</v>
       </c>
       <c r="F12" t="n">
-        <v>8.140700000000001</v>
+        <v>8.140699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>5.740699999999999</v>
+        <v>5.7407</v>
       </c>
       <c r="H12" t="n">
         <v>-5.7342</v>
@@ -1372,7 +1372,7 @@
         <v>1.4666</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5957</v>
+        <v>1.595699999999999</v>
       </c>
       <c r="N12" t="n">
         <v>-8.412699999999999</v>
@@ -1387,19 +1387,19 @@
         <v>-20.6631</v>
       </c>
       <c r="R12" t="n">
-        <v>8.700099999999999</v>
+        <v>8.700100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>3.484900000000001</v>
+        <v>5.1973</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3184999999999999</v>
+        <v>2.0308</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1664</v>
+        <v>3.1663</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8896</v>
+        <v>4.889599999999998</v>
       </c>
       <c r="W12" t="n">
         <v>10.211</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4679</v>
+        <v>4.9294</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2784</v>
+        <v>2.0742</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1895</v>
+        <v>2.8552</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3455</v>
+        <v>3.794</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9814</v>
+        <v>2.9685</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6359</v>
+        <v>0.8255</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4372</v>
+        <v>3.7216</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4372</v>
+        <v>2.7072</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.0144</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0917</v>
+        <v>0.0723</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5442</v>
+        <v>0.2612</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6359</v>
+        <v>-0.1889</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1751</v>
+        <v>2.8276</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0773</v>
+        <v>0.1349</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8411999999999999</v>
+        <v>-0.0156</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2361</v>
+        <v>0.1505</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7997</v>
+        <v>4.7922</v>
       </c>
       <c r="E14" t="n">
-        <v>2.186</v>
+        <v>3.6079</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6137</v>
+        <v>1.1844</v>
       </c>
       <c r="G14" t="n">
-        <v>3.794</v>
+        <v>3.3455</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9685</v>
+        <v>3.9814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8255</v>
+        <v>-0.6359</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7216</v>
+        <v>3.4372</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7072</v>
+        <v>3.4372</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0144</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0723</v>
+        <v>-0.0917</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2612</v>
+        <v>0.5442</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1889</v>
+        <v>-0.6359</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8276</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0052</v>
+        <v>0.4017</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0961</v>
+        <v>0.1707</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.091</v>
+        <v>0.231</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6443</v>
+        <v>2.9359</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7335</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9107</v>
+        <v>2.0906</v>
       </c>
       <c r="G15" t="n">
         <v>0.3018</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0479</v>
+        <v>0.2436</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3064</v>
+        <v>-0.1947</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2585</v>
+        <v>0.4383</v>
       </c>
       <c r="V15" t="n">
         <v>1.5204</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.149</v>
+        <v>0.4156</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.5733</v>
       </c>
       <c r="F16" t="n">
-        <v>0.149</v>
+        <v>0.989</v>
       </c>
       <c r="G16" t="n">
-        <v>0.149</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.149</v>
+        <v>0.885</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.4664</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.2404</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.7068</v>
       </c>
       <c r="M16" t="n">
-        <v>0.149</v>
+        <v>1.0072</v>
       </c>
       <c r="N16" t="n">
-        <v>0.149</v>
+        <v>0.6446</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.3626</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.0403</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.1069</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0185</v>
+        <v>0.149</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7969000000000001</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7783</v>
+        <v>0.149</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="H17" t="n">
-        <v>0.885</v>
+        <v>0.149</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3442</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2404</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7068</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0072</v>
+        <v>0.149</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6446</v>
+        <v>0.149</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3626</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4744</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.144</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3593</v>
+        <v>-0.0202</v>
       </c>
       <c r="E18" t="n">
         <v>-1.5287</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1694</v>
+        <v>1.5084</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3404</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0189</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>-0.5888</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4301</v>
+        <v>-0.091</v>
       </c>
       <c r="V18" t="n">
         <v>1.695</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8703</v>
+        <v>-1.4441</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5014</v>
+        <v>-1.4721</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6311</v>
+        <v>0.028</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3628</v>
+        <v>-2.9252</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0181</v>
+        <v>-0.5657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3809</v>
+        <v>-2.3595</v>
       </c>
       <c r="J19" t="n">
-        <v>1.249</v>
+        <v>-1.1585</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2108</v>
+        <v>0.3317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-1.4901</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8863</v>
+        <v>-1.7668</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2289</v>
+        <v>-0.8974</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3426</v>
+        <v>-0.8694</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4624</v>
+        <v>-0.4765</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0529</v>
+        <v>-0.3136</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5153</v>
+        <v>-0.1628</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5945</v>
+        <v>-1.6872</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8074</v>
+        <v>-1.9485</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2129</v>
+        <v>0.2613</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9252</v>
+        <v>0.3628</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5657</v>
+        <v>-0.0181</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3595</v>
+        <v>0.3809</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1585</v>
+        <v>1.249</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3317</v>
+        <v>1.2108</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4901</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7668</v>
+        <v>-0.8863</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8974</v>
+        <v>-1.2289</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8694</v>
+        <v>0.3426</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9576</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6268</v>
+        <v>-0.3545</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6489</v>
+        <v>-0.4999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0221</v>
+        <v>0.1454</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9938</v>
+        <v>-1.6893</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2606</v>
+        <v>-1.9253</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2668</v>
+        <v>0.2359</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4235</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8101</v>
+        <v>-0.5056</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0479</v>
+        <v>-0.7126</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2378</v>
+        <v>0.207</v>
       </c>
       <c r="V21" t="n">
         <v>0.3698</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0803</v>
+        <v>-1.7579</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2676</v>
+        <v>-1.1559</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8127</v>
+        <v>-0.6021</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8703</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4504</v>
+        <v>-0.128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1935</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2569</v>
+        <v>-0.0463</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4997</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.2964</v>
+        <v>-8.0306</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1762</v>
+        <v>-6.0644</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1202</v>
+        <v>-1.9661</v>
       </c>
       <c r="G23" t="n">
         <v>-4.675</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6013</v>
+        <v>-1.3354</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9349</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6663</v>
+        <v>-0.5122</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4552</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.152200000000001</v>
+        <v>-1.407199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.140899999999998</v>
+        <v>-8.140799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5.9885</v>
+        <v>6.7336</v>
       </c>
       <c r="G24" t="n">
         <v>-5.7405</v>
@@ -2326,13 +2326,13 @@
         <v>20.6634</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.4849</v>
+        <v>-2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.1665</v>
+        <v>-3.1662</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3185</v>
+        <v>0.4266</v>
       </c>
       <c r="V24" t="n">
         <v>-4.8895</v>
